--- a/files/PhDTimelineTemplate.xlsx
+++ b/files/PhDTimelineTemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uvic-my.sharepoint.com/personal/kss_uvic_ca/Documents/Desktop/PHDO-assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="8_{A983111C-028E-DC4E-8DA8-CBC6248F10F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E97D43AE-5A9E-524E-8202-700603AA01EF}"/>
+  <xr:revisionPtr revIDLastSave="79" documentId="8_{A983111C-028E-DC4E-8DA8-CBC6248F10F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4684635-0058-B94B-B90E-C94D40FC70D7}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="600" windowWidth="50120" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -91,19 +91,8 @@
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Meet with Chair of Focused Field Examining Committee to discuss format of examination question paper (15 working days prior to exam).</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">
+          </rPr>
+          <t xml:space="preserve">Meet with Chair of Focused Field Examining Committee to discuss format of examination question paper (15 working days prior to exam).
 </t>
         </r>
       </text>
@@ -342,19 +331,8 @@
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Personal notes to myself about my broader goals for even doing a PhD in the first place. Think of these as guiding principles.</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">
+          </rPr>
+          <t xml:space="preserve">Personal notes to myself about my broader goals for even doing a PhD in the first place. Think of these as guiding principles.
 </t>
         </r>
       </text>
@@ -856,7 +834,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -916,6 +894,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -945,9 +938,6 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1042,6 +1032,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1064,10 +1057,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1313,63 +1302,63 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28">
+      <c r="B1" s="27">
         <v>2018</v>
       </c>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="37">
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="36">
         <v>2019</v>
       </c>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
-      <c r="R1" s="38">
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="37">
         <v>2020</v>
       </c>
-      <c r="S1" s="29"/>
-      <c r="T1" s="29"/>
-      <c r="U1" s="29"/>
-      <c r="V1" s="29"/>
-      <c r="W1" s="29"/>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="29"/>
-      <c r="AA1" s="29"/>
-      <c r="AB1" s="29"/>
-      <c r="AC1" s="29"/>
-      <c r="AD1" s="39">
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
+      <c r="V1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="28"/>
+      <c r="Y1" s="28"/>
+      <c r="Z1" s="28"/>
+      <c r="AA1" s="28"/>
+      <c r="AB1" s="28"/>
+      <c r="AC1" s="28"/>
+      <c r="AD1" s="38">
         <v>2021</v>
       </c>
-      <c r="AE1" s="29"/>
-      <c r="AF1" s="29"/>
-      <c r="AG1" s="29"/>
-      <c r="AH1" s="29"/>
-      <c r="AI1" s="29"/>
-      <c r="AJ1" s="29"/>
-      <c r="AK1" s="29"/>
-      <c r="AL1" s="29"/>
-      <c r="AM1" s="29"/>
-      <c r="AN1" s="29"/>
-      <c r="AO1" s="29"/>
-      <c r="AP1" s="28">
+      <c r="AE1" s="28"/>
+      <c r="AF1" s="28"/>
+      <c r="AG1" s="28"/>
+      <c r="AH1" s="28"/>
+      <c r="AI1" s="28"/>
+      <c r="AJ1" s="28"/>
+      <c r="AK1" s="28"/>
+      <c r="AL1" s="28"/>
+      <c r="AM1" s="28"/>
+      <c r="AN1" s="28"/>
+      <c r="AO1" s="28"/>
+      <c r="AP1" s="27">
         <v>2022</v>
       </c>
-      <c r="AQ1" s="29"/>
-      <c r="AR1" s="29"/>
-      <c r="AS1" s="29"/>
-      <c r="AT1" s="29"/>
-      <c r="AU1" s="29"/>
-      <c r="AV1" s="29"/>
+      <c r="AQ1" s="28"/>
+      <c r="AR1" s="28"/>
+      <c r="AS1" s="28"/>
+      <c r="AT1" s="28"/>
+      <c r="AU1" s="28"/>
+      <c r="AV1" s="28"/>
     </row>
     <row r="2" spans="1:48" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
@@ -1516,863 +1505,863 @@
       </c>
     </row>
     <row r="3" spans="1:48" ht="112" x14ac:dyDescent="0.2">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8" t="s">
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8" t="s">
+      <c r="L3" s="7"/>
+      <c r="M3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="9" t="s">
+      <c r="O3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8" t="s">
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="R3" s="8" t="s">
+      <c r="R3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="S3" s="8" t="s">
+      <c r="S3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="T3" s="8" t="s">
+      <c r="T3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="U3" s="8"/>
-      <c r="V3" s="10"/>
-      <c r="W3" s="8" t="s">
+      <c r="U3" s="7"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="X3" s="8"/>
-      <c r="Y3" s="8" t="s">
+      <c r="X3" s="7"/>
+      <c r="Y3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="Z3" s="10"/>
-      <c r="AA3" s="10"/>
-      <c r="AB3" s="8"/>
-      <c r="AC3" s="8" t="s">
+      <c r="Z3" s="9"/>
+      <c r="AA3" s="9"/>
+      <c r="AB3" s="7"/>
+      <c r="AC3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AD3" s="8"/>
-      <c r="AE3" s="8" t="s">
+      <c r="AD3" s="7"/>
+      <c r="AE3" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="AF3" s="8"/>
-      <c r="AG3" s="8"/>
-      <c r="AH3" s="8"/>
-      <c r="AI3" s="8" t="s">
+      <c r="AF3" s="7"/>
+      <c r="AG3" s="7"/>
+      <c r="AH3" s="7"/>
+      <c r="AI3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="AJ3" s="8"/>
-      <c r="AK3" s="11"/>
-      <c r="AL3" s="11"/>
-      <c r="AM3" s="11"/>
-      <c r="AN3" s="11"/>
-      <c r="AO3" s="11"/>
-      <c r="AP3" s="11"/>
-      <c r="AQ3" s="11"/>
-      <c r="AR3" s="11"/>
-      <c r="AS3" s="11"/>
-      <c r="AT3" s="11"/>
-      <c r="AU3" s="11"/>
-      <c r="AV3" s="30" t="s">
+      <c r="AJ3" s="7"/>
+      <c r="AK3" s="10"/>
+      <c r="AL3" s="10"/>
+      <c r="AM3" s="10"/>
+      <c r="AN3" s="10"/>
+      <c r="AO3" s="10"/>
+      <c r="AP3" s="10"/>
+      <c r="AQ3" s="10"/>
+      <c r="AR3" s="10"/>
+      <c r="AS3" s="10"/>
+      <c r="AT3" s="10"/>
+      <c r="AU3" s="10"/>
+      <c r="AV3" s="29" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:48" ht="64" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="13" t="s">
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="N4" s="12"/>
-      <c r="O4" s="12"/>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12"/>
-      <c r="S4" s="12"/>
-      <c r="T4" s="12"/>
-      <c r="U4" s="12"/>
-      <c r="V4" s="12"/>
-      <c r="W4" s="12"/>
-      <c r="X4" s="12"/>
-      <c r="Y4" s="13" t="s">
+      <c r="N4" s="11"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="11"/>
+      <c r="S4" s="11"/>
+      <c r="T4" s="11"/>
+      <c r="U4" s="11"/>
+      <c r="V4" s="11"/>
+      <c r="W4" s="11"/>
+      <c r="X4" s="11"/>
+      <c r="Y4" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="Z4" s="12"/>
-      <c r="AA4" s="12"/>
-      <c r="AB4" s="12"/>
-      <c r="AC4" s="12"/>
-      <c r="AD4" s="12"/>
-      <c r="AE4" s="12"/>
-      <c r="AF4" s="12"/>
-      <c r="AG4" s="12"/>
-      <c r="AH4" s="12"/>
-      <c r="AI4" s="12"/>
-      <c r="AJ4" s="12"/>
-      <c r="AK4" s="14" t="s">
+      <c r="Z4" s="11"/>
+      <c r="AA4" s="11"/>
+      <c r="AB4" s="11"/>
+      <c r="AC4" s="11"/>
+      <c r="AD4" s="11"/>
+      <c r="AE4" s="11"/>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="11"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="AL4" s="11"/>
-      <c r="AM4" s="11"/>
-      <c r="AN4" s="11"/>
-      <c r="AO4" s="11"/>
-      <c r="AP4" s="11"/>
-      <c r="AQ4" s="11"/>
-      <c r="AR4" s="11"/>
-      <c r="AS4" s="11"/>
-      <c r="AT4" s="8"/>
-      <c r="AU4" s="8"/>
-      <c r="AV4" s="31"/>
+      <c r="AL4" s="10"/>
+      <c r="AM4" s="10"/>
+      <c r="AN4" s="10"/>
+      <c r="AO4" s="10"/>
+      <c r="AP4" s="10"/>
+      <c r="AQ4" s="10"/>
+      <c r="AR4" s="10"/>
+      <c r="AS4" s="10"/>
+      <c r="AT4" s="7"/>
+      <c r="AU4" s="7"/>
+      <c r="AV4" s="30"/>
     </row>
     <row r="5" spans="1:48" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="40" t="s">
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="8"/>
-      <c r="R5" s="8"/>
-      <c r="S5" s="8"/>
-      <c r="T5" s="8"/>
-      <c r="U5" s="8"/>
-      <c r="V5" s="8"/>
-      <c r="W5" s="8"/>
-      <c r="X5" s="8"/>
-      <c r="Y5" s="8"/>
-      <c r="Z5" s="8"/>
-      <c r="AA5" s="8"/>
-      <c r="AB5" s="8"/>
-      <c r="AC5" s="8"/>
-      <c r="AD5" s="8"/>
-      <c r="AE5" s="8"/>
-      <c r="AF5" s="8"/>
-      <c r="AG5" s="8"/>
-      <c r="AH5" s="8"/>
-      <c r="AI5" s="8"/>
-      <c r="AJ5" s="8"/>
-      <c r="AK5" s="11"/>
-      <c r="AL5" s="11"/>
-      <c r="AM5" s="11"/>
-      <c r="AN5" s="11"/>
-      <c r="AO5" s="11"/>
-      <c r="AP5" s="11"/>
-      <c r="AQ5" s="11"/>
-      <c r="AR5" s="11"/>
-      <c r="AS5" s="11"/>
-      <c r="AT5" s="11"/>
-      <c r="AU5" s="11"/>
-      <c r="AV5" s="31"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7"/>
+      <c r="Z5" s="7"/>
+      <c r="AA5" s="7"/>
+      <c r="AB5" s="7"/>
+      <c r="AC5" s="7"/>
+      <c r="AD5" s="7"/>
+      <c r="AE5" s="7"/>
+      <c r="AF5" s="7"/>
+      <c r="AG5" s="7"/>
+      <c r="AH5" s="7"/>
+      <c r="AI5" s="7"/>
+      <c r="AJ5" s="7"/>
+      <c r="AK5" s="10"/>
+      <c r="AL5" s="10"/>
+      <c r="AM5" s="10"/>
+      <c r="AN5" s="10"/>
+      <c r="AO5" s="10"/>
+      <c r="AP5" s="10"/>
+      <c r="AQ5" s="10"/>
+      <c r="AR5" s="10"/>
+      <c r="AS5" s="10"/>
+      <c r="AT5" s="10"/>
+      <c r="AU5" s="10"/>
+      <c r="AV5" s="30"/>
     </row>
     <row r="6" spans="1:48" ht="48" x14ac:dyDescent="0.2">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="8" t="s">
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="10"/>
-      <c r="Q6" s="8" t="s">
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="8"/>
-      <c r="U6" s="8"/>
-      <c r="V6" s="8"/>
-      <c r="W6" s="8"/>
-      <c r="X6" s="15"/>
-      <c r="Y6" s="8"/>
-      <c r="Z6" s="8"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="8"/>
-      <c r="AF6" s="8"/>
-      <c r="AG6" s="8"/>
-      <c r="AH6" s="8"/>
-      <c r="AI6" s="8"/>
-      <c r="AJ6" s="8"/>
-      <c r="AK6" s="11"/>
-      <c r="AL6" s="11"/>
-      <c r="AM6" s="11"/>
-      <c r="AN6" s="11"/>
-      <c r="AO6" s="11"/>
-      <c r="AP6" s="11"/>
-      <c r="AQ6" s="11"/>
-      <c r="AR6" s="11"/>
-      <c r="AS6" s="11"/>
-      <c r="AT6" s="11"/>
-      <c r="AU6" s="11"/>
-      <c r="AV6" s="31"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7"/>
+      <c r="X6" s="14"/>
+      <c r="Y6" s="7"/>
+      <c r="Z6" s="7"/>
+      <c r="AA6" s="7"/>
+      <c r="AB6" s="7"/>
+      <c r="AC6" s="7"/>
+      <c r="AD6" s="7"/>
+      <c r="AE6" s="7"/>
+      <c r="AF6" s="7"/>
+      <c r="AG6" s="7"/>
+      <c r="AH6" s="7"/>
+      <c r="AI6" s="7"/>
+      <c r="AJ6" s="7"/>
+      <c r="AK6" s="10"/>
+      <c r="AL6" s="10"/>
+      <c r="AM6" s="10"/>
+      <c r="AN6" s="10"/>
+      <c r="AO6" s="10"/>
+      <c r="AP6" s="10"/>
+      <c r="AQ6" s="10"/>
+      <c r="AR6" s="10"/>
+      <c r="AS6" s="10"/>
+      <c r="AT6" s="10"/>
+      <c r="AU6" s="10"/>
+      <c r="AV6" s="30"/>
     </row>
     <row r="7" spans="1:48" ht="64" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="16" t="s">
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="8"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="10"/>
-      <c r="U7" s="16" t="s">
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="V7" s="8"/>
-      <c r="W7" s="8"/>
-      <c r="X7" s="10"/>
-      <c r="Y7" s="8"/>
-      <c r="Z7" s="8"/>
-      <c r="AA7" s="8"/>
-      <c r="AB7" s="8"/>
-      <c r="AC7" s="8" t="s">
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="7"/>
+      <c r="Z7" s="7"/>
+      <c r="AA7" s="7"/>
+      <c r="AB7" s="7"/>
+      <c r="AC7" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AD7" s="16" t="s">
+      <c r="AD7" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="AE7" s="17" t="s">
+      <c r="AE7" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="AF7" s="10"/>
-      <c r="AG7" s="8"/>
-      <c r="AH7" s="8"/>
-      <c r="AI7" s="8"/>
-      <c r="AJ7" s="18"/>
-      <c r="AK7" s="11"/>
-      <c r="AL7" s="11"/>
-      <c r="AM7" s="11"/>
-      <c r="AN7" s="11"/>
-      <c r="AO7" s="11"/>
-      <c r="AP7" s="11"/>
-      <c r="AQ7" s="11"/>
-      <c r="AR7" s="11"/>
-      <c r="AS7" s="11"/>
-      <c r="AT7" s="16" t="s">
+      <c r="AF7" s="9"/>
+      <c r="AG7" s="7"/>
+      <c r="AH7" s="7"/>
+      <c r="AI7" s="7"/>
+      <c r="AJ7" s="17"/>
+      <c r="AK7" s="10"/>
+      <c r="AL7" s="10"/>
+      <c r="AM7" s="10"/>
+      <c r="AN7" s="10"/>
+      <c r="AO7" s="10"/>
+      <c r="AP7" s="10"/>
+      <c r="AQ7" s="10"/>
+      <c r="AR7" s="10"/>
+      <c r="AS7" s="10"/>
+      <c r="AT7" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="AU7" s="16" t="s">
+      <c r="AU7" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="AV7" s="31"/>
+      <c r="AV7" s="30"/>
     </row>
     <row r="8" spans="1:48" ht="64" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="8"/>
-      <c r="S8" s="8"/>
-      <c r="T8" s="8"/>
-      <c r="U8" s="8"/>
-      <c r="V8" s="8"/>
-      <c r="W8" s="15"/>
-      <c r="X8" s="8"/>
-      <c r="Y8" s="8"/>
-      <c r="Z8" s="8"/>
-      <c r="AA8" s="8"/>
-      <c r="AB8" s="8"/>
-      <c r="AC8" s="8"/>
-      <c r="AD8" s="8"/>
-      <c r="AE8" s="8" t="s">
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="14"/>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="7"/>
+      <c r="Z8" s="7"/>
+      <c r="AA8" s="7"/>
+      <c r="AB8" s="7"/>
+      <c r="AC8" s="7"/>
+      <c r="AD8" s="7"/>
+      <c r="AE8" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="AF8" s="8" t="s">
+      <c r="AF8" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="AG8" s="8" t="s">
+      <c r="AG8" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="AH8" s="8" t="s">
+      <c r="AH8" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="AI8" s="8" t="s">
+      <c r="AI8" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="AJ8" s="8"/>
-      <c r="AK8" s="8" t="s">
+      <c r="AJ8" s="7"/>
+      <c r="AK8" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="AL8" s="8" t="s">
+      <c r="AL8" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="AM8" s="8" t="s">
+      <c r="AM8" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="AN8" s="8"/>
-      <c r="AO8" s="8"/>
-      <c r="AP8" s="8" t="s">
+      <c r="AN8" s="7"/>
+      <c r="AO8" s="7"/>
+      <c r="AP8" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="AQ8" s="8" t="s">
+      <c r="AQ8" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="AR8" s="8"/>
-      <c r="AS8" s="8" t="s">
+      <c r="AR8" s="7"/>
+      <c r="AS8" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="AT8" s="8"/>
-      <c r="AU8" s="8"/>
-      <c r="AV8" s="31"/>
+      <c r="AT8" s="7"/>
+      <c r="AU8" s="7"/>
+      <c r="AV8" s="30"/>
     </row>
     <row r="9" spans="1:48" ht="48" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-      <c r="S9" s="10"/>
-      <c r="T9" s="10"/>
-      <c r="U9" s="8"/>
-      <c r="V9" s="8"/>
-      <c r="W9" s="8"/>
-      <c r="X9" s="8"/>
-      <c r="Y9" s="8"/>
-      <c r="Z9" s="8"/>
-      <c r="AA9" s="8"/>
-      <c r="AB9" s="8"/>
-      <c r="AC9" s="8"/>
-      <c r="AD9" s="8"/>
-      <c r="AE9" s="8"/>
-      <c r="AF9" s="10"/>
-      <c r="AG9" s="8"/>
-      <c r="AH9" s="8"/>
-      <c r="AI9" s="10"/>
-      <c r="AJ9" s="8"/>
-      <c r="AK9" s="11"/>
-      <c r="AL9" s="11"/>
-      <c r="AM9" s="11"/>
-      <c r="AN9" s="11"/>
-      <c r="AO9" s="11"/>
-      <c r="AP9" s="19" t="s">
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="9"/>
+      <c r="T9" s="9"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="7"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7"/>
+      <c r="Z9" s="7"/>
+      <c r="AA9" s="7"/>
+      <c r="AB9" s="7"/>
+      <c r="AC9" s="7"/>
+      <c r="AD9" s="7"/>
+      <c r="AE9" s="7"/>
+      <c r="AF9" s="9"/>
+      <c r="AG9" s="7"/>
+      <c r="AH9" s="7"/>
+      <c r="AI9" s="9"/>
+      <c r="AJ9" s="7"/>
+      <c r="AK9" s="10"/>
+      <c r="AL9" s="10"/>
+      <c r="AM9" s="10"/>
+      <c r="AN9" s="10"/>
+      <c r="AO9" s="10"/>
+      <c r="AP9" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="AQ9" s="19"/>
-      <c r="AR9" s="11"/>
-      <c r="AS9" s="11"/>
-      <c r="AT9" s="11"/>
-      <c r="AU9" s="11"/>
-      <c r="AV9" s="31"/>
+      <c r="AQ9" s="18"/>
+      <c r="AR9" s="10"/>
+      <c r="AS9" s="10"/>
+      <c r="AT9" s="10"/>
+      <c r="AU9" s="10"/>
+      <c r="AV9" s="30"/>
     </row>
     <row r="10" spans="1:48" ht="15" x14ac:dyDescent="0.2">
-      <c r="A10" s="20"/>
-      <c r="B10" s="33"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="29"/>
-      <c r="O10" s="29"/>
-      <c r="P10" s="29"/>
-      <c r="Q10" s="29"/>
-      <c r="R10" s="29"/>
-      <c r="S10" s="29"/>
-      <c r="T10" s="29"/>
-      <c r="U10" s="29"/>
-      <c r="V10" s="29"/>
-      <c r="W10" s="29"/>
-      <c r="X10" s="29"/>
-      <c r="Y10" s="29"/>
-      <c r="Z10" s="29"/>
-      <c r="AA10" s="29"/>
-      <c r="AB10" s="29"/>
-      <c r="AC10" s="29"/>
-      <c r="AD10" s="29"/>
-      <c r="AE10" s="29"/>
-      <c r="AF10" s="29"/>
-      <c r="AG10" s="29"/>
-      <c r="AH10" s="29"/>
-      <c r="AI10" s="29"/>
-      <c r="AJ10" s="29"/>
-      <c r="AK10" s="29"/>
-      <c r="AL10" s="33"/>
-      <c r="AM10" s="29"/>
-      <c r="AN10" s="29"/>
-      <c r="AO10" s="29"/>
-      <c r="AP10" s="29"/>
-      <c r="AQ10" s="29"/>
-      <c r="AR10" s="29"/>
-      <c r="AS10" s="29"/>
-      <c r="AT10" s="29"/>
-      <c r="AU10" s="29"/>
-      <c r="AV10" s="29"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
+      <c r="K10" s="28"/>
+      <c r="L10" s="28"/>
+      <c r="M10" s="28"/>
+      <c r="N10" s="28"/>
+      <c r="O10" s="28"/>
+      <c r="P10" s="28"/>
+      <c r="Q10" s="28"/>
+      <c r="R10" s="28"/>
+      <c r="S10" s="28"/>
+      <c r="T10" s="28"/>
+      <c r="U10" s="28"/>
+      <c r="V10" s="28"/>
+      <c r="W10" s="28"/>
+      <c r="X10" s="28"/>
+      <c r="Y10" s="28"/>
+      <c r="Z10" s="28"/>
+      <c r="AA10" s="28"/>
+      <c r="AB10" s="28"/>
+      <c r="AC10" s="28"/>
+      <c r="AD10" s="28"/>
+      <c r="AE10" s="28"/>
+      <c r="AF10" s="28"/>
+      <c r="AG10" s="28"/>
+      <c r="AH10" s="28"/>
+      <c r="AI10" s="28"/>
+      <c r="AJ10" s="28"/>
+      <c r="AK10" s="28"/>
+      <c r="AL10" s="32"/>
+      <c r="AM10" s="28"/>
+      <c r="AN10" s="28"/>
+      <c r="AO10" s="28"/>
+      <c r="AP10" s="28"/>
+      <c r="AQ10" s="28"/>
+      <c r="AR10" s="28"/>
+      <c r="AS10" s="28"/>
+      <c r="AT10" s="28"/>
+      <c r="AU10" s="28"/>
+      <c r="AV10" s="28"/>
     </row>
     <row r="11" spans="1:48" ht="64" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="B11" s="41" t="s">
+      <c r="B11" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="41" t="s">
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="J11" s="29"/>
-      <c r="K11" s="8" t="s">
+      <c r="J11" s="28"/>
+      <c r="K11" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="L11" s="41" t="s">
+      <c r="L11" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="M11" s="29"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="8"/>
-      <c r="S11" s="8"/>
-      <c r="T11" s="8"/>
-      <c r="U11" s="8"/>
-      <c r="V11" s="8"/>
-      <c r="W11" s="8"/>
-      <c r="X11" s="8"/>
-      <c r="Y11" s="8"/>
-      <c r="Z11" s="8"/>
-      <c r="AA11" s="8"/>
-      <c r="AB11" s="8"/>
-      <c r="AC11" s="8"/>
-      <c r="AD11" s="8" t="s">
+      <c r="M11" s="28"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="7"/>
+      <c r="X11" s="7"/>
+      <c r="Y11" s="7"/>
+      <c r="Z11" s="7"/>
+      <c r="AA11" s="7"/>
+      <c r="AB11" s="7"/>
+      <c r="AC11" s="7"/>
+      <c r="AD11" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="AE11" s="8"/>
-      <c r="AF11" s="8"/>
-      <c r="AG11" s="8"/>
-      <c r="AH11" s="8"/>
-      <c r="AI11" s="8"/>
-      <c r="AJ11" s="8"/>
-      <c r="AK11" s="8" t="s">
+      <c r="AE11" s="7"/>
+      <c r="AF11" s="7"/>
+      <c r="AG11" s="7"/>
+      <c r="AH11" s="7"/>
+      <c r="AI11" s="7"/>
+      <c r="AJ11" s="7"/>
+      <c r="AK11" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="AL11" s="8"/>
-      <c r="AM11" s="8"/>
-      <c r="AN11" s="8"/>
-      <c r="AO11" s="8"/>
-      <c r="AP11" s="8"/>
-      <c r="AQ11" s="8"/>
-      <c r="AR11" s="8"/>
-      <c r="AS11" s="8"/>
-      <c r="AT11" s="8"/>
-      <c r="AU11" s="8"/>
-      <c r="AV11" s="22" t="s">
+      <c r="AL11" s="7"/>
+      <c r="AM11" s="7"/>
+      <c r="AN11" s="7"/>
+      <c r="AO11" s="7"/>
+      <c r="AP11" s="7"/>
+      <c r="AQ11" s="7"/>
+      <c r="AR11" s="7"/>
+      <c r="AS11" s="7"/>
+      <c r="AT11" s="7"/>
+      <c r="AU11" s="7"/>
+      <c r="AV11" s="21" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:48" ht="64" x14ac:dyDescent="0.2">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="21" t="s">
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="L12" s="21" t="s">
+      <c r="L12" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="M12" s="21"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="8"/>
-      <c r="S12" s="8"/>
-      <c r="T12" s="8"/>
-      <c r="U12" s="8"/>
-      <c r="V12" s="21" t="s">
+      <c r="M12" s="20"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="7"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="W12" s="21" t="s">
+      <c r="W12" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="X12" s="21" t="s">
+      <c r="X12" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="Y12" s="8"/>
-      <c r="Z12" s="8"/>
-      <c r="AA12" s="8"/>
-      <c r="AB12" s="8"/>
-      <c r="AC12" s="8"/>
-      <c r="AD12" s="8"/>
-      <c r="AE12" s="8"/>
-      <c r="AF12" s="8"/>
-      <c r="AG12" s="8"/>
-      <c r="AH12" s="8"/>
-      <c r="AI12" s="8"/>
-      <c r="AJ12" s="21" t="s">
+      <c r="Y12" s="7"/>
+      <c r="Z12" s="7"/>
+      <c r="AA12" s="7"/>
+      <c r="AB12" s="7"/>
+      <c r="AC12" s="7"/>
+      <c r="AD12" s="7"/>
+      <c r="AE12" s="7"/>
+      <c r="AF12" s="7"/>
+      <c r="AG12" s="7"/>
+      <c r="AH12" s="7"/>
+      <c r="AI12" s="7"/>
+      <c r="AJ12" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="AK12" s="8"/>
-      <c r="AL12" s="8"/>
-      <c r="AM12" s="8"/>
-      <c r="AN12" s="8"/>
-      <c r="AO12" s="21" t="s">
+      <c r="AK12" s="7"/>
+      <c r="AL12" s="7"/>
+      <c r="AM12" s="7"/>
+      <c r="AN12" s="7"/>
+      <c r="AO12" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="AP12" s="8"/>
-      <c r="AQ12" s="8"/>
-      <c r="AR12" s="8"/>
-      <c r="AS12" s="8"/>
-      <c r="AT12" s="8"/>
-      <c r="AU12" s="8"/>
+      <c r="AP12" s="7"/>
+      <c r="AQ12" s="7"/>
+      <c r="AR12" s="7"/>
+      <c r="AS12" s="7"/>
+      <c r="AT12" s="7"/>
+      <c r="AU12" s="7"/>
     </row>
     <row r="13" spans="1:48" ht="15" x14ac:dyDescent="0.2">
-      <c r="A13" s="20"/>
-      <c r="B13" s="33"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="29"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="29"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="29"/>
-      <c r="N13" s="29"/>
-      <c r="O13" s="29"/>
-      <c r="P13" s="29"/>
-      <c r="Q13" s="29"/>
-      <c r="R13" s="29"/>
-      <c r="S13" s="29"/>
-      <c r="T13" s="29"/>
-      <c r="U13" s="29"/>
-      <c r="V13" s="29"/>
-      <c r="W13" s="29"/>
-      <c r="X13" s="29"/>
-      <c r="Y13" s="29"/>
-      <c r="Z13" s="29"/>
-      <c r="AA13" s="29"/>
-      <c r="AB13" s="29"/>
-      <c r="AC13" s="29"/>
-      <c r="AD13" s="29"/>
-      <c r="AE13" s="29"/>
-      <c r="AF13" s="29"/>
-      <c r="AG13" s="29"/>
-      <c r="AH13" s="29"/>
-      <c r="AI13" s="29"/>
-      <c r="AJ13" s="29"/>
-      <c r="AK13" s="29"/>
-      <c r="AL13" s="20"/>
-      <c r="AM13" s="20"/>
-      <c r="AN13" s="20"/>
-      <c r="AO13" s="20"/>
-      <c r="AP13" s="20"/>
-      <c r="AQ13" s="20"/>
-      <c r="AR13" s="20"/>
-      <c r="AS13" s="20"/>
-      <c r="AT13" s="20"/>
-      <c r="AU13" s="20"/>
-      <c r="AV13" s="20"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="28"/>
+      <c r="M13" s="28"/>
+      <c r="N13" s="28"/>
+      <c r="O13" s="28"/>
+      <c r="P13" s="28"/>
+      <c r="Q13" s="28"/>
+      <c r="R13" s="28"/>
+      <c r="S13" s="28"/>
+      <c r="T13" s="28"/>
+      <c r="U13" s="28"/>
+      <c r="V13" s="28"/>
+      <c r="W13" s="28"/>
+      <c r="X13" s="28"/>
+      <c r="Y13" s="28"/>
+      <c r="Z13" s="28"/>
+      <c r="AA13" s="28"/>
+      <c r="AB13" s="28"/>
+      <c r="AC13" s="28"/>
+      <c r="AD13" s="28"/>
+      <c r="AE13" s="28"/>
+      <c r="AF13" s="28"/>
+      <c r="AG13" s="28"/>
+      <c r="AH13" s="28"/>
+      <c r="AI13" s="28"/>
+      <c r="AJ13" s="28"/>
+      <c r="AK13" s="28"/>
+      <c r="AL13" s="19"/>
+      <c r="AM13" s="19"/>
+      <c r="AN13" s="19"/>
+      <c r="AO13" s="19"/>
+      <c r="AP13" s="19"/>
+      <c r="AQ13" s="19"/>
+      <c r="AR13" s="19"/>
+      <c r="AS13" s="19"/>
+      <c r="AT13" s="19"/>
+      <c r="AU13" s="19"/>
+      <c r="AV13" s="19"/>
     </row>
     <row r="14" spans="1:48" ht="34" x14ac:dyDescent="0.2">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="B14" s="34"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="36"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="8"/>
-      <c r="S14" s="8"/>
-      <c r="T14" s="8"/>
-      <c r="U14" s="8"/>
-      <c r="V14" s="8"/>
-      <c r="W14" s="8"/>
-      <c r="X14" s="8"/>
-      <c r="Y14" s="8"/>
-      <c r="Z14" s="8"/>
-      <c r="AA14" s="8"/>
-      <c r="AB14" s="8"/>
-      <c r="AC14" s="8"/>
-      <c r="AD14" s="8"/>
-      <c r="AE14" s="8"/>
-      <c r="AF14" s="8"/>
-      <c r="AG14" s="8"/>
-      <c r="AH14" s="8"/>
-      <c r="AI14" s="8"/>
-      <c r="AJ14" s="8"/>
-      <c r="AK14" s="15"/>
-      <c r="AL14" s="15"/>
-      <c r="AM14" s="15"/>
-      <c r="AN14" s="15"/>
-      <c r="AO14" s="15"/>
-      <c r="AP14" s="15"/>
-      <c r="AQ14" s="15"/>
-      <c r="AR14" s="15"/>
-      <c r="AS14" s="15"/>
-      <c r="AT14" s="15"/>
-      <c r="AU14" s="15"/>
-      <c r="AV14" s="15"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="34"/>
+      <c r="J14" s="35"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="7"/>
+      <c r="W14" s="7"/>
+      <c r="X14" s="7"/>
+      <c r="Y14" s="7"/>
+      <c r="Z14" s="7"/>
+      <c r="AA14" s="7"/>
+      <c r="AB14" s="7"/>
+      <c r="AC14" s="7"/>
+      <c r="AD14" s="7"/>
+      <c r="AE14" s="7"/>
+      <c r="AF14" s="7"/>
+      <c r="AG14" s="7"/>
+      <c r="AH14" s="7"/>
+      <c r="AI14" s="7"/>
+      <c r="AJ14" s="7"/>
+      <c r="AK14" s="14"/>
+      <c r="AL14" s="14"/>
+      <c r="AM14" s="14"/>
+      <c r="AN14" s="14"/>
+      <c r="AO14" s="14"/>
+      <c r="AP14" s="14"/>
+      <c r="AQ14" s="14"/>
+      <c r="AR14" s="14"/>
+      <c r="AS14" s="14"/>
+      <c r="AT14" s="14"/>
+      <c r="AU14" s="14"/>
+      <c r="AV14" s="14"/>
     </row>
     <row r="15" spans="1:48" ht="102" x14ac:dyDescent="0.2">
-      <c r="A15" s="25" t="s">
+      <c r="A15" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="C15" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="D15" s="23" t="s">
+      <c r="D15" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="E15" s="23" t="s">
+      <c r="E15" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="23"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="8"/>
-      <c r="S15" s="8"/>
-      <c r="T15" s="8"/>
-      <c r="U15" s="8"/>
-      <c r="V15" s="8"/>
-      <c r="W15" s="8"/>
-      <c r="X15" s="8"/>
-      <c r="Y15" s="8"/>
-      <c r="Z15" s="8"/>
-      <c r="AA15" s="8"/>
-      <c r="AB15" s="8"/>
-      <c r="AC15" s="8"/>
-      <c r="AD15" s="8"/>
-      <c r="AE15" s="8"/>
-      <c r="AF15" s="8"/>
-      <c r="AG15" s="8"/>
-      <c r="AH15" s="8"/>
-      <c r="AI15" s="8"/>
-      <c r="AJ15" s="8"/>
-      <c r="AK15" s="15"/>
-      <c r="AL15" s="15"/>
-      <c r="AM15" s="15"/>
-      <c r="AN15" s="15"/>
-      <c r="AO15" s="15"/>
-      <c r="AP15" s="15"/>
-      <c r="AQ15" s="15"/>
-      <c r="AR15" s="15"/>
-      <c r="AS15" s="15"/>
-      <c r="AT15" s="15"/>
-      <c r="AU15" s="15"/>
-      <c r="AV15" s="15"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="7"/>
+      <c r="W15" s="7"/>
+      <c r="X15" s="7"/>
+      <c r="Y15" s="7"/>
+      <c r="Z15" s="7"/>
+      <c r="AA15" s="7"/>
+      <c r="AB15" s="7"/>
+      <c r="AC15" s="7"/>
+      <c r="AD15" s="7"/>
+      <c r="AE15" s="7"/>
+      <c r="AF15" s="7"/>
+      <c r="AG15" s="7"/>
+      <c r="AH15" s="7"/>
+      <c r="AI15" s="7"/>
+      <c r="AJ15" s="7"/>
+      <c r="AK15" s="14"/>
+      <c r="AL15" s="14"/>
+      <c r="AM15" s="14"/>
+      <c r="AN15" s="14"/>
+      <c r="AO15" s="14"/>
+      <c r="AP15" s="14"/>
+      <c r="AQ15" s="14"/>
+      <c r="AR15" s="14"/>
+      <c r="AS15" s="14"/>
+      <c r="AT15" s="14"/>
+      <c r="AU15" s="14"/>
+      <c r="AV15" s="14"/>
     </row>
     <row r="16" spans="1:48" ht="68" x14ac:dyDescent="0.2">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="F16" s="24" t="s">
+      <c r="F16" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="G16" s="24" t="s">
+      <c r="G16" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="H16" s="24" t="s">
+      <c r="H16" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="I16" s="24" t="s">
+      <c r="I16" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="J16" s="24" t="s">
+      <c r="J16" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8"/>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="8"/>
-      <c r="S16" s="8"/>
-      <c r="T16" s="8"/>
-      <c r="U16" s="8"/>
-      <c r="V16" s="8"/>
-      <c r="W16" s="8"/>
-      <c r="X16" s="8"/>
-      <c r="Y16" s="8"/>
-      <c r="Z16" s="8"/>
-      <c r="AA16" s="8"/>
-      <c r="AB16" s="8"/>
-      <c r="AC16" s="8"/>
-      <c r="AD16" s="8"/>
-      <c r="AE16" s="8"/>
-      <c r="AF16" s="8"/>
-      <c r="AG16" s="8"/>
-      <c r="AH16" s="8"/>
-      <c r="AI16" s="8"/>
-      <c r="AJ16" s="8"/>
-      <c r="AK16" s="15"/>
-      <c r="AL16" s="15"/>
-      <c r="AM16" s="15"/>
-      <c r="AN16" s="15"/>
-      <c r="AO16" s="15"/>
-      <c r="AP16" s="15"/>
-      <c r="AQ16" s="15"/>
-      <c r="AR16" s="15"/>
-      <c r="AS16" s="15"/>
-      <c r="AT16" s="15"/>
-      <c r="AU16" s="15"/>
-      <c r="AV16" s="15"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="7"/>
+      <c r="W16" s="7"/>
+      <c r="X16" s="7"/>
+      <c r="Y16" s="7"/>
+      <c r="Z16" s="7"/>
+      <c r="AA16" s="7"/>
+      <c r="AB16" s="7"/>
+      <c r="AC16" s="7"/>
+      <c r="AD16" s="7"/>
+      <c r="AE16" s="7"/>
+      <c r="AF16" s="7"/>
+      <c r="AG16" s="7"/>
+      <c r="AH16" s="7"/>
+      <c r="AI16" s="7"/>
+      <c r="AJ16" s="7"/>
+      <c r="AK16" s="14"/>
+      <c r="AL16" s="14"/>
+      <c r="AM16" s="14"/>
+      <c r="AN16" s="14"/>
+      <c r="AO16" s="14"/>
+      <c r="AP16" s="14"/>
+      <c r="AQ16" s="14"/>
+      <c r="AR16" s="14"/>
+      <c r="AS16" s="14"/>
+      <c r="AT16" s="14"/>
+      <c r="AU16" s="14"/>
+      <c r="AV16" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="15">
